--- a/reports/Debug-snowbowl-20260106/For The Week Ending (Prior Year)_Visits.xlsx
+++ b/reports/Debug-snowbowl-20260106/For The Week Ending (Prior Year)_Visits.xlsx
@@ -34,13 +34,13 @@
     <t>Snowbowl Passes</t>
   </si>
   <si>
+    <t>Snowbowl Comp Tickets</t>
+  </si>
+  <si>
+    <t>Snowbowl Uplift Tickets</t>
+  </si>
+  <si>
     <t>Snowbowl Tickets</t>
-  </si>
-  <si>
-    <t>Snowbowl Uplift Tickets</t>
-  </si>
-  <si>
-    <t>Snowbowl Comp Tickets</t>
   </si>
 </sst>
 </file>
@@ -431,10 +431,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>45664</v>
+        <v>45663</v>
       </c>
       <c r="C2" s="2">
-        <v>565</v>
+        <v>6</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -445,10 +445,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>45664</v>
+        <v>45663</v>
       </c>
       <c r="C3" s="2">
-        <v>1702</v>
+        <v>287</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>6</v>
@@ -462,7 +462,7 @@
         <v>45663</v>
       </c>
       <c r="C4" s="2">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>5</v>
@@ -473,13 +473,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2">
-        <v>45663</v>
+        <v>45664</v>
       </c>
       <c r="C5" s="2">
-        <v>1828</v>
+        <v>4</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -487,13 +487,13 @@
         <v>1</v>
       </c>
       <c r="B6" s="2">
-        <v>45664</v>
+        <v>45663</v>
       </c>
       <c r="C6" s="2">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -504,10 +504,10 @@
         <v>45664</v>
       </c>
       <c r="C7" s="2">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -518,7 +518,7 @@
         <v>45663</v>
       </c>
       <c r="C8" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>5</v>
@@ -532,10 +532,10 @@
         <v>45663</v>
       </c>
       <c r="C9" s="2">
-        <v>287</v>
+        <v>749</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -543,13 +543,13 @@
         <v>1</v>
       </c>
       <c r="B10" s="2">
-        <v>45663</v>
+        <v>45664</v>
       </c>
       <c r="C10" s="2">
-        <v>63</v>
+        <v>565</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -560,10 +560,10 @@
         <v>45664</v>
       </c>
       <c r="C11" s="2">
-        <v>59</v>
+        <v>1702</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -571,13 +571,13 @@
         <v>1</v>
       </c>
       <c r="B12" s="2">
-        <v>45664</v>
+        <v>45663</v>
       </c>
       <c r="C12" s="2">
-        <v>161</v>
+        <v>6</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -588,10 +588,10 @@
         <v>45663</v>
       </c>
       <c r="C13" s="2">
-        <v>47</v>
+        <v>1828</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -613,13 +613,13 @@
         <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>45663</v>
+        <v>45664</v>
       </c>
       <c r="C15" s="2">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -627,13 +627,13 @@
         <v>1</v>
       </c>
       <c r="B16" s="2">
-        <v>45663</v>
+        <v>45664</v>
       </c>
       <c r="C16" s="2">
-        <v>749</v>
+        <v>161</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
